--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEBRASKA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEBRASKA_2017.xlsx
@@ -427,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="5">
@@ -1003,7 +1003,7 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="37">
@@ -1057,7 +1057,7 @@
         <v>4</v>
       </c>
       <c r="D39">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="40">
@@ -1597,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="D69">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="70">
@@ -1633,7 +1633,7 @@
         <v>4</v>
       </c>
       <c r="D71">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="72">
@@ -1705,7 +1705,7 @@
         <v>4</v>
       </c>
       <c r="D75">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="76">
@@ -1741,7 +1741,7 @@
         <v>4</v>
       </c>
       <c r="D77">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="78">
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
       <c r="D92">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="93">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C121">
         <v>4</v>
       </c>
       <c r="D121">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="122">
@@ -2641,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="D127">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="128">
@@ -2659,7 +2659,7 @@
         <v>4</v>
       </c>
       <c r="D128">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="129">
@@ -3109,7 +3109,7 @@
         <v>4</v>
       </c>
       <c r="D153">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="154">
@@ -3163,7 +3163,7 @@
         <v>4</v>
       </c>
       <c r="D156">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="157">
@@ -3595,7 +3595,7 @@
         <v>4</v>
       </c>
       <c r="D180">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="181">
@@ -3667,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="D184">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="185">
@@ -3901,7 +3901,7 @@
         <v>4</v>
       </c>
       <c r="D197">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="198">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C198">
@@ -3991,7 +3991,7 @@
         <v>4</v>
       </c>
       <c r="D202">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="203">
@@ -4315,7 +4315,7 @@
         <v>4</v>
       </c>
       <c r="D220">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="221">
@@ -4603,7 +4603,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="237">
@@ -4639,7 +4639,7 @@
         <v>4</v>
       </c>
       <c r="D238">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="239">
@@ -4675,7 +4675,7 @@
         <v>4</v>
       </c>
       <c r="D240">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="241">
@@ -4927,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="D254">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="255">
@@ -5269,7 +5269,7 @@
         <v>4</v>
       </c>
       <c r="D273">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="274">
@@ -5575,7 +5575,7 @@
         <v>4</v>
       </c>
       <c r="D290">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="291">
@@ -5971,7 +5971,7 @@
         <v>4</v>
       </c>
       <c r="D312">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="313">
@@ -6151,7 +6151,7 @@
         <v>4</v>
       </c>
       <c r="D322">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="323">
@@ -6385,7 +6385,7 @@
         <v>4</v>
       </c>
       <c r="D335">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="336">
@@ -6601,7 +6601,7 @@
         <v>4</v>
       </c>
       <c r="D347">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="348">
@@ -7213,7 +7213,7 @@
         <v>4</v>
       </c>
       <c r="D381">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="382">
@@ -7285,7 +7285,7 @@
         <v>4</v>
       </c>
       <c r="D385">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="386">
@@ -7393,7 +7393,7 @@
         <v>4</v>
       </c>
       <c r="D391">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="392">
@@ -7735,7 +7735,7 @@
         <v>4</v>
       </c>
       <c r="D410">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="411">
@@ -7915,7 +7915,7 @@
         <v>4</v>
       </c>
       <c r="D420">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="421">
@@ -8365,7 +8365,7 @@
         <v>4</v>
       </c>
       <c r="D445">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="446">
@@ -8401,7 +8401,7 @@
         <v>4</v>
       </c>
       <c r="D447">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="448">
@@ -8437,7 +8437,7 @@
         <v>4</v>
       </c>
       <c r="D449">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="450">
@@ -8563,7 +8563,7 @@
         <v>4</v>
       </c>
       <c r="D456">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="457">
@@ -8617,7 +8617,7 @@
         <v>4</v>
       </c>
       <c r="D459">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="460">
@@ -8743,7 +8743,7 @@
         <v>4</v>
       </c>
       <c r="D466">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="467">
@@ -9229,7 +9229,7 @@
         <v>4</v>
       </c>
       <c r="D493">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="494">
@@ -9265,7 +9265,7 @@
         <v>4</v>
       </c>
       <c r="D495">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="496">
@@ -9319,7 +9319,7 @@
         <v>4</v>
       </c>
       <c r="D498">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="499">
@@ -9355,7 +9355,7 @@
         <v>4</v>
       </c>
       <c r="D500">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="501">
@@ -9373,7 +9373,7 @@
         <v>4</v>
       </c>
       <c r="D501">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="502">
@@ -9553,7 +9553,7 @@
         <v>4</v>
       </c>
       <c r="D511">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="512">
@@ -9931,7 +9931,7 @@
         <v>4</v>
       </c>
       <c r="D532">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="533">
@@ -10255,7 +10255,7 @@
         <v>4</v>
       </c>
       <c r="D550">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="551">
@@ -10453,7 +10453,7 @@
         <v>4</v>
       </c>
       <c r="D561">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="562">
@@ -11317,7 +11317,7 @@
         <v>4</v>
       </c>
       <c r="D609">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="610">
@@ -12001,7 +12001,7 @@
         <v>4</v>
       </c>
       <c r="D647">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="648">
@@ -12073,7 +12073,7 @@
         <v>4</v>
       </c>
       <c r="D651">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="652">
@@ -12253,7 +12253,7 @@
         <v>4</v>
       </c>
       <c r="D661">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="662">
@@ -12343,7 +12343,7 @@
         <v>4</v>
       </c>
       <c r="D666">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="667">
@@ -12487,7 +12487,7 @@
         <v>4</v>
       </c>
       <c r="D674">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="675">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C687">
@@ -13783,7 +13783,7 @@
         <v>4</v>
       </c>
       <c r="D746">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="747">
@@ -13819,7 +13819,7 @@
         <v>4</v>
       </c>
       <c r="D748">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="749">
@@ -14215,7 +14215,7 @@
         <v>4</v>
       </c>
       <c r="D770">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="771">
@@ -14287,7 +14287,7 @@
         <v>4</v>
       </c>
       <c r="D774">
-        <v>0.0009599232061435085</v>
+        <v>0.0009599232061435084</v>
       </c>
     </row>
     <row r="775">
